--- a/AC_2018/AC_029_029-Siricilla.xlsx
+++ b/AC_2018/AC_029_029-Siricilla.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,19 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +70,32 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +117,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +177,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,11 +563,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -518,102 +616,107 @@
           <t>PS_No</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>PS_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Avunoori Ramakanth Rao</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Kalvakuntla Taraka Rama Rao (K.T.R.)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Mallugari Narsa Goud</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>K.K. Mahender Reddy</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Karingula Yadagiri</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Kurapati Ramesh</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Gouta Ganesh Gangaputhra</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Choutapelli Venugopal</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Thakkala Kiran</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Dosala Chandram</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Srinivas Boinpally</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Alwala Kanakaraju (AKR)</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Koduri Bala Lingam</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Total_Valid_Votes</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Rejected_Votes</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Checksum_Diff</t>
         </is>
@@ -623,237 +726,257 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Vanpalli</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>627</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="K6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O6" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="S6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="4" t="n">
         <v>966</v>
       </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" s="4" t="n">
-        <v>779</v>
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <f>SUM(C6:P6)-Q6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>2</v>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Garjanapalli</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>381</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="F7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>417</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>613</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="T7" s="4" t="n">
         <v>618</v>
       </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" s="4" t="n">
-        <v>288</v>
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <f>SUM(C7:P7)-Q7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Garjanapalli</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="D8" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>556</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>845</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="S8" s="4" t="n">
+      <c r="T8" s="4" t="n">
         <v>866</v>
       </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" s="4" t="n">
-        <v>-24</v>
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <f>SUM(C8:P8)-Q8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Adavipadira</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>607</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
@@ -864,11 +987,11 @@
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" s="4" t="n">
         <v>0</v>
       </c>
@@ -876,37 +999,43 @@
         <v>0</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>830</v>
+        <v>0</v>
+      </c>
+      <c r="V9" s="4">
+        <f>SUM(C9:P9)-Q9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Maddimalla</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>415</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
       </c>
@@ -923,61 +1052,67 @@
         <v>0</v>
       </c>
       <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>559</v>
       </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
         <v>565</v>
       </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" s="4" t="n">
-        <v>298</v>
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <f>SUM(C10:P10)-Q10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Veernapalli</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>303</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
       </c>
@@ -988,129 +1123,141 @@
         <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>479</v>
       </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
         <v>487</v>
       </c>
-      <c r="T11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
+      </c>
+      <c r="V11" s="4">
+        <f>SUM(C11:P11)-Q11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Veernapalli</t>
+        </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>393</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="G12" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="I12" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>590</v>
       </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
         <v>597</v>
       </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
+        <f>SUM(C12:P12)-Q12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Kancharla</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>483</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" s="4" t="n">
         <v>0</v>
       </c>
@@ -1121,58 +1268,64 @@
         <v>0</v>
       </c>
       <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>694</v>
       </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>708</v>
       </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" s="4" t="n">
-        <v>-173</v>
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
+        <f>SUM(C13:P13)-Q13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Rangampet H/o Kancharla</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>655</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
       </c>
@@ -1180,52 +1333,58 @@
         <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>906</v>
       </c>
-      <c r="Q14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="S14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-67</v>
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
+        <f>SUM(C14:P14)-Q14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Almaspur</t>
+        </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H15" s="4" t="n">
         <v>2</v>
       </c>
@@ -1233,48 +1392,54 @@
         <v>2</v>
       </c>
       <c r="J15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="P15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="Q15" s="4" t="n">
         <v>641</v>
       </c>
-      <c r="Q15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="T15" s="4" t="n">
         <v>651</v>
       </c>
-      <c r="T15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" s="4" t="n">
-        <v>-519</v>
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <f>SUM(C15:P15)-Q15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Almaspur</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>0</v>
@@ -1286,37 +1451,37 @@
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
@@ -1325,39 +1490,45 @@
         <v>0</v>
       </c>
       <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4" t="n">
         <v>926</v>
       </c>
-      <c r="T16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" s="4" t="n">
-        <v>231</v>
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <f>SUM(C16:P16)-Q16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Akkapalli</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>418</v>
       </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>4</v>
@@ -1366,141 +1537,153 @@
         <v>4</v>
       </c>
       <c r="K17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L17" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N17" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="P17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>632</v>
       </c>
-      <c r="Q17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="S17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-22</v>
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
+        <f>SUM(C17:P17)-Q17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>0</v>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Dumala</t>
+        </is>
       </c>
       <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J18" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="S18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="4" t="n">
         <v>781</v>
       </c>
-      <c r="T18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
+        <f>SUM(C18:P18)-Q18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>0</v>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Dumala</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>327</v>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="L19" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" s="4" t="n">
         <v>0</v>
       </c>
@@ -1511,30 +1694,36 @@
         <v>0</v>
       </c>
       <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="Q19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="S19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>299</v>
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <f>SUM(C19:P19)-Q19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>0</v>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Rajannapet</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>0</v>
@@ -1549,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>0</v>
@@ -1564,11 +1753,11 @@
         <v>0</v>
       </c>
       <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
       </c>
@@ -1585,21 +1774,27 @@
         <v>0</v>
       </c>
       <c r="S20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4" t="n">
         <v>492</v>
       </c>
-      <c r="T20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="V20" s="4">
+        <f>SUM(C20:P20)-Q20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Rajannapet</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>0</v>
@@ -1611,14 +1806,14 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" s="4" t="n">
         <v>0</v>
       </c>
@@ -1626,13 +1821,13 @@
         <v>0</v>
       </c>
       <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L21" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M21" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1641,11 +1836,11 @@
         <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>652</v>
       </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" s="4" t="n">
         <v>0</v>
       </c>
@@ -1656,15 +1851,21 @@
         <v>0</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-462</v>
+        <v>0</v>
+      </c>
+      <c r="V21" s="4">
+        <f>SUM(C21:P21)-Q21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>0</v>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Gollapalli</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>0</v>
@@ -1676,26 +1877,26 @@
         <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="J22" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="4" t="n">
         <v>0</v>
       </c>
@@ -1715,86 +1916,98 @@
         <v>0</v>
       </c>
       <c r="S22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4" t="n">
         <v>977</v>
       </c>
-      <c r="T22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" s="4" t="n">
-        <v>193</v>
+        <v>0</v>
+      </c>
+      <c r="V22" s="4">
+        <f>SUM(C22:P22)-Q22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Gollapalli</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>413</v>
       </c>
-      <c r="E23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="O23" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>631</v>
       </c>
-      <c r="Q23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="4" t="n">
         <v>638</v>
       </c>
-      <c r="T23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" s="4" t="n">
-        <v>-196</v>
+        <v>0</v>
+      </c>
+      <c r="V23" s="4">
+        <f>SUM(C23:P23)-Q23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Racharla Boppapur</t>
+        </is>
       </c>
       <c r="C24" s="4" t="n">
         <v>0</v>
@@ -1806,11 +2019,11 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
@@ -1818,26 +2031,26 @@
         <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
@@ -1848,18 +2061,24 @@
         <v>0</v>
       </c>
       <c r="T24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="4" t="n">
-        <v>147</v>
+      <c r="V24" s="4">
+        <f>SUM(C24:P24)-Q24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>0</v>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Thimmapur</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>0</v>
@@ -1868,14 +2087,14 @@
         <v>0</v>
       </c>
       <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>462</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
@@ -1883,48 +2102,54 @@
         <v>0</v>
       </c>
       <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="O25" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="P25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="Q25" s="4" t="n">
         <v>607</v>
       </c>
-      <c r="Q25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="S25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="U25" s="4" t="n">
-        <v>-126</v>
+      <c r="V25" s="4">
+        <f>SUM(C25:P25)-Q25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Gundaram</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>0</v>
@@ -1936,35 +2161,35 @@
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M26" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="N26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" s="4" t="n">
         <v>0</v>
       </c>
@@ -1981,15 +2206,21 @@
         <v>0</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="V26" s="4">
+        <f>SUM(C26:P26)-Q26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>0</v>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Gajasingavaram</t>
+        </is>
       </c>
       <c r="C27" s="4" t="n">
         <v>0</v>
@@ -2001,34 +2232,34 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>486</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>7</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>0</v>
@@ -2046,15 +2277,21 @@
         <v>0</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>514</v>
+        <v>0</v>
+      </c>
+      <c r="V27" s="4">
+        <f>SUM(C27:P27)-Q27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Gajasingavaram</t>
+        </is>
       </c>
       <c r="C28" s="4" t="n">
         <v>0</v>
@@ -2063,16 +2300,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>285</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
@@ -2081,10 +2318,10 @@
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>2</v>
@@ -2093,11 +2330,11 @@
         <v>2</v>
       </c>
       <c r="O28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="P28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q28" s="4" t="n">
         <v>0</v>
       </c>
@@ -2111,19 +2348,25 @@
         <v>0</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>341</v>
+        <v>0</v>
+      </c>
+      <c r="V28" s="4">
+        <f>SUM(C28:P28)-Q28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Sarampalli</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="C29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D29" s="4" t="n">
         <v>0</v>
       </c>
@@ -2146,11 +2389,11 @@
         <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" s="4" t="n">
         <v>0</v>
       </c>
@@ -2158,37 +2401,43 @@
         <v>0</v>
       </c>
       <c r="O29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="Q29" s="4" t="n">
         <v>671</v>
       </c>
-      <c r="Q29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="S29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-447</v>
+        <v>0</v>
+      </c>
+      <c r="V29" s="4">
+        <f>SUM(C29:P29)-Q29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
         <v>214</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Desaipalli</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
         <v>214</v>
       </c>
-      <c r="C30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D30" s="4" t="n">
         <v>0</v>
       </c>
@@ -2223,14 +2472,14 @@
         <v>0</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="4" t="n">
         <v>820</v>
       </c>
-      <c r="Q30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" s="4" t="n">
         <v>0</v>
       </c>
@@ -2241,19 +2490,25 @@
         <v>0</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-604</v>
+        <v>0</v>
+      </c>
+      <c r="V30" s="4">
+        <f>SUM(C30:P30)-Q30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Baddenapalli</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="C31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D31" s="4" t="n">
         <v>0</v>
       </c>
@@ -2276,45 +2531,51 @@
         <v>0</v>
       </c>
       <c r="K31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="Q31" s="4" t="n">
         <v>736</v>
       </c>
-      <c r="Q31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="T31" s="4" t="n">
         <v>744</v>
       </c>
-      <c r="T31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U31" s="4" t="n">
-        <v>-505</v>
+        <v>0</v>
+      </c>
+      <c r="V31" s="4">
+        <f>SUM(C31:P31)-Q31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>0</v>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Ramannapalli</t>
+        </is>
       </c>
       <c r="C32" s="4" t="n">
         <v>0</v>
@@ -2329,11 +2590,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" s="4" t="n">
         <v>0</v>
       </c>
@@ -2341,52 +2602,58 @@
         <v>0</v>
       </c>
       <c r="K32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L32" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="M32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>560</v>
       </c>
-      <c r="Q32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="S32" s="4" t="n">
+      <c r="T32" s="4" t="n">
         <v>574</v>
       </c>
-      <c r="T32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U32" s="4" t="n">
-        <v>-540</v>
+        <v>0</v>
+      </c>
+      <c r="V32" s="4">
+        <f>SUM(C32:P32)-Q32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
         <v>217</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>0</v>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Baswapur</t>
+        </is>
       </c>
       <c r="C33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E33" s="4" t="n">
         <v>0</v>
       </c>
@@ -2394,11 +2661,11 @@
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" s="4" t="n">
         <v>0</v>
       </c>
@@ -2406,22 +2673,22 @@
         <v>0</v>
       </c>
       <c r="K33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="L33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O33" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="P33" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="4" t="n">
         <v>0</v>
@@ -2430,95 +2697,260 @@
         <v>0</v>
       </c>
       <c r="S33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="4" t="n">
         <v>460</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="U33" s="4" t="n">
-        <v>20</v>
+      <c r="V33" s="4">
+        <f>SUM(C33:P33)-Q33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B34" s="6">
-        <f>SUM(B6:B33)</f>
-        <v/>
-      </c>
-      <c r="C34" s="6">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr"/>
+      <c r="C34" s="8">
         <f>SUM(C6:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="8">
         <f>SUM(D6:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="8">
         <f>SUM(E6:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="8">
         <f>SUM(F6:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="8">
         <f>SUM(G6:G33)</f>
         <v/>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="8">
         <f>SUM(H6:H33)</f>
         <v/>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="8">
         <f>SUM(I6:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="8">
         <f>SUM(J6:J33)</f>
         <v/>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="8">
         <f>SUM(K6:K33)</f>
         <v/>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="8">
         <f>SUM(L6:L33)</f>
         <v/>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="8">
         <f>SUM(M6:M33)</f>
         <v/>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="8">
         <f>SUM(N6:N33)</f>
         <v/>
       </c>
-      <c r="O34" s="6">
+      <c r="O34" s="8">
         <f>SUM(O6:O33)</f>
         <v/>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="8">
         <f>SUM(P6:P33)</f>
         <v/>
       </c>
-      <c r="Q34" s="6">
+      <c r="Q34" s="8">
         <f>SUM(Q6:Q33)</f>
         <v/>
       </c>
-      <c r="R34" s="6">
+      <c r="R34" s="8">
         <f>SUM(R6:R33)</f>
         <v/>
       </c>
-      <c r="S34" s="6">
+      <c r="S34" s="8">
         <f>SUM(S6:S33)</f>
         <v/>
       </c>
-      <c r="T34" s="6">
+      <c r="T34" s="8">
         <f>SUM(T6:T33)</f>
+        <v/>
+      </c>
+      <c r="U34" s="8">
+        <f>SUM(U6:U33)</f>
+        <v/>
+      </c>
+      <c r="V34" s="8">
+        <f>SUM(V6:V33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr"/>
+      <c r="C35" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>378</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>307</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <v>732</v>
+      </c>
+      <c r="R35" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S35" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="10" t="n">
+        <v>739</v>
+      </c>
+      <c r="U35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr"/>
+      <c r="C36" s="12">
+        <f>C34+C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="12">
+        <f>D34+D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="12">
+        <f>E34+E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="12">
+        <f>F34+F35</f>
+        <v/>
+      </c>
+      <c r="G36" s="12">
+        <f>G34+G35</f>
+        <v/>
+      </c>
+      <c r="H36" s="12">
+        <f>H34+H35</f>
+        <v/>
+      </c>
+      <c r="I36" s="12">
+        <f>I34+I35</f>
+        <v/>
+      </c>
+      <c r="J36" s="12">
+        <f>J34+J35</f>
+        <v/>
+      </c>
+      <c r="K36" s="12">
+        <f>K34+K35</f>
+        <v/>
+      </c>
+      <c r="L36" s="12">
+        <f>L34+L35</f>
+        <v/>
+      </c>
+      <c r="M36" s="12">
+        <f>M34+M35</f>
+        <v/>
+      </c>
+      <c r="N36" s="12">
+        <f>N34+N35</f>
+        <v/>
+      </c>
+      <c r="O36" s="12">
+        <f>O34+O35</f>
+        <v/>
+      </c>
+      <c r="P36" s="12">
+        <f>P34+P35</f>
+        <v/>
+      </c>
+      <c r="Q36" s="12">
+        <f>Q34+Q35</f>
+        <v/>
+      </c>
+      <c r="R36" s="12">
+        <f>R34+R35</f>
+        <v/>
+      </c>
+      <c r="S36" s="12">
+        <f>S34+S35</f>
+        <v/>
+      </c>
+      <c r="T36" s="12">
+        <f>T34+T35</f>
+        <v/>
+      </c>
+      <c r="U36" s="12">
+        <f>U34+U35</f>
+        <v/>
+      </c>
+      <c r="V36" s="12">
+        <f>V34+V35</f>
         <v/>
       </c>
     </row>
